--- a/us/processed/state_per_disease/Ｑ熱.xlsx
+++ b/us/processed/state_per_disease/Ｑ熱.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P59"/>
+  <dimension ref="A1:R59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -508,6 +508,16 @@
           <t>2026-W15</t>
         </is>
       </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -560,6 +570,12 @@
       <c r="P2" t="n">
         <v>0</v>
       </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -612,6 +628,12 @@
       <c r="P3" t="n">
         <v>0</v>
       </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -664,6 +686,12 @@
       <c r="P4" t="n">
         <v>0</v>
       </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -716,6 +744,12 @@
       <c r="P5" t="n">
         <v>0</v>
       </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -768,6 +802,12 @@
       <c r="P6" t="n">
         <v>2</v>
       </c>
+      <c r="Q6" t="n">
+        <v>2</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -820,6 +860,12 @@
       <c r="P7" t="n">
         <v>38</v>
       </c>
+      <c r="Q7" t="n">
+        <v>44</v>
+      </c>
+      <c r="R7" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -872,6 +918,12 @@
       <c r="P8" t="n">
         <v>2</v>
       </c>
+      <c r="Q8" t="n">
+        <v>2</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -924,6 +976,12 @@
       <c r="P9" t="n">
         <v>0</v>
       </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -976,6 +1034,12 @@
       <c r="P10" t="n">
         <v>0</v>
       </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1028,6 +1092,12 @@
       <c r="P11" t="n">
         <v>0</v>
       </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1080,6 +1150,12 @@
       <c r="P12" t="n">
         <v>0</v>
       </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1132,6 +1208,12 @@
       <c r="P13" t="n">
         <v>2</v>
       </c>
+      <c r="Q13" t="n">
+        <v>2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1184,6 +1266,12 @@
       <c r="P14" t="n">
         <v>0</v>
       </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1236,6 +1324,12 @@
       <c r="P15" t="n">
         <v>0</v>
       </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1288,6 +1382,12 @@
       <c r="P16" t="n">
         <v>0</v>
       </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1340,6 +1440,12 @@
       <c r="P17" t="n">
         <v>0</v>
       </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1392,6 +1498,12 @@
       <c r="P18" t="n">
         <v>0</v>
       </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1444,6 +1556,12 @@
       <c r="P19" t="n">
         <v>0</v>
       </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1496,6 +1614,12 @@
       <c r="P20" t="n">
         <v>0</v>
       </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1548,6 +1672,12 @@
       <c r="P21" t="n">
         <v>2</v>
       </c>
+      <c r="Q21" t="n">
+        <v>2</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1600,6 +1730,12 @@
       <c r="P22" t="n">
         <v>0</v>
       </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1652,6 +1788,12 @@
       <c r="P23" t="n">
         <v>0</v>
       </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1704,6 +1846,12 @@
       <c r="P24" t="n">
         <v>0</v>
       </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1756,6 +1904,12 @@
       <c r="P25" t="n">
         <v>0</v>
       </c>
+      <c r="Q25" t="n">
+        <v>2</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1808,6 +1962,12 @@
       <c r="P26" t="n">
         <v>0</v>
       </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1860,6 +2020,12 @@
       <c r="P27" t="n">
         <v>0</v>
       </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1912,6 +2078,12 @@
       <c r="P28" t="n">
         <v>0</v>
       </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1964,6 +2136,12 @@
       <c r="P29" t="n">
         <v>0</v>
       </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2016,6 +2194,12 @@
       <c r="P30" t="n">
         <v>0</v>
       </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2068,6 +2252,12 @@
       <c r="P31" t="n">
         <v>0</v>
       </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2120,6 +2310,12 @@
       <c r="P32" t="n">
         <v>2</v>
       </c>
+      <c r="Q32" t="n">
+        <v>2</v>
+      </c>
+      <c r="R32" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2172,6 +2368,12 @@
       <c r="P33" t="n">
         <v>0</v>
       </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2224,6 +2426,12 @@
       <c r="P34" t="n">
         <v>0</v>
       </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2276,6 +2484,12 @@
       <c r="P35" t="n">
         <v>0</v>
       </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2328,6 +2542,12 @@
       <c r="P36" t="n">
         <v>0</v>
       </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2380,6 +2600,12 @@
       <c r="P37" t="n">
         <v>0</v>
       </c>
+      <c r="Q37" t="n">
+        <v>2</v>
+      </c>
+      <c r="R37" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2432,6 +2658,12 @@
       <c r="P38" t="n">
         <v>0</v>
       </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2484,6 +2716,12 @@
       <c r="P39" t="n">
         <v>0</v>
       </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2536,6 +2774,12 @@
       <c r="P40" t="n">
         <v>0</v>
       </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2588,6 +2832,12 @@
       <c r="P41" t="n">
         <v>0</v>
       </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2640,6 +2890,12 @@
       <c r="P42" t="n">
         <v>0</v>
       </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2692,6 +2948,12 @@
       <c r="P43" t="n">
         <v>2</v>
       </c>
+      <c r="Q43" t="n">
+        <v>6</v>
+      </c>
+      <c r="R43" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2744,6 +3006,12 @@
       <c r="P44" t="n">
         <v>2</v>
       </c>
+      <c r="Q44" t="n">
+        <v>2</v>
+      </c>
+      <c r="R44" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2796,6 +3064,12 @@
       <c r="P45" t="n">
         <v>0</v>
       </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2848,6 +3122,12 @@
       <c r="P46" t="n">
         <v>0</v>
       </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2900,6 +3180,12 @@
       <c r="P47" t="n">
         <v>0</v>
       </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2952,6 +3238,12 @@
       <c r="P48" t="n">
         <v>0</v>
       </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3004,6 +3296,12 @@
       <c r="P49" t="n">
         <v>0</v>
       </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3056,6 +3354,12 @@
       <c r="P50" t="n">
         <v>2</v>
       </c>
+      <c r="Q50" t="n">
+        <v>2</v>
+      </c>
+      <c r="R50" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3108,6 +3412,12 @@
       <c r="P51" t="n">
         <v>0</v>
       </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3160,6 +3470,12 @@
       <c r="P52" t="n">
         <v>0</v>
       </c>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3212,6 +3528,12 @@
       <c r="P53" t="n">
         <v>0</v>
       </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3264,6 +3586,12 @@
       <c r="P54" t="n">
         <v>0</v>
       </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3316,6 +3644,12 @@
       <c r="P55" t="n">
         <v>2</v>
       </c>
+      <c r="Q55" t="n">
+        <v>2</v>
+      </c>
+      <c r="R55" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3368,6 +3702,12 @@
       <c r="P56" t="n">
         <v>0</v>
       </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3420,6 +3760,12 @@
       <c r="P57" t="n">
         <v>0</v>
       </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3472,6 +3818,12 @@
       <c r="P58" t="n">
         <v>0</v>
       </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3522,6 +3874,12 @@
         <v>2</v>
       </c>
       <c r="P59" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>2</v>
+      </c>
+      <c r="R59" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3611,7 +3969,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8">
@@ -3911,7 +4269,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
@@ -3971,7 +4329,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44">
